--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,418 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113496671</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80063</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>330839</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6418137</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113495813</v>
+      </c>
+      <c r="B6" t="n">
+        <v>95962</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mollsjönäs 390 , Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>330577</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6417835</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113496459</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90041</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupevik (Djupevik), Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>330713</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6418187</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113497853</v>
+      </c>
+      <c r="B8" t="n">
+        <v>74126</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>330551</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6417874</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113496671</v>
+        <v>113495813</v>
       </c>
       <c r="B5" t="n">
-        <v>80063</v>
+        <v>95984</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330839</v>
+        <v>330577</v>
       </c>
       <c r="R5" t="n">
-        <v>6418137</v>
+        <v>6417835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113495813</v>
+        <v>113496459</v>
       </c>
       <c r="B6" t="n">
-        <v>95962</v>
+        <v>90063</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330577</v>
+        <v>330713</v>
       </c>
       <c r="R6" t="n">
-        <v>6417835</v>
+        <v>6418187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113496459</v>
+        <v>113497853</v>
       </c>
       <c r="B7" t="n">
-        <v>90041</v>
+        <v>74148</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330713</v>
+        <v>330551</v>
       </c>
       <c r="R7" t="n">
-        <v>6418187</v>
+        <v>6417874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113497853</v>
+        <v>113496671</v>
       </c>
       <c r="B8" t="n">
-        <v>74126</v>
+        <v>80085</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,39 +1336,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330551</v>
+        <v>330839</v>
       </c>
       <c r="R8" t="n">
-        <v>6417874</v>
+        <v>6418137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113495813</v>
+        <v>113497853</v>
       </c>
       <c r="B5" t="n">
-        <v>95984</v>
+        <v>74151</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330577</v>
+        <v>330551</v>
       </c>
       <c r="R5" t="n">
-        <v>6417835</v>
+        <v>6417874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113496459</v>
+        <v>113496671</v>
       </c>
       <c r="B6" t="n">
-        <v>90063</v>
+        <v>80089</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1130,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330713</v>
+        <v>330839</v>
       </c>
       <c r="R6" t="n">
-        <v>6418187</v>
+        <v>6418137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113497853</v>
+        <v>113495813</v>
       </c>
       <c r="B7" t="n">
-        <v>74148</v>
+        <v>95988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330551</v>
+        <v>330577</v>
       </c>
       <c r="R7" t="n">
-        <v>6417874</v>
+        <v>6417835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113496671</v>
+        <v>113496459</v>
       </c>
       <c r="B8" t="n">
-        <v>80085</v>
+        <v>90067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,39 +1336,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330839</v>
+        <v>330713</v>
       </c>
       <c r="R8" t="n">
-        <v>6418137</v>
+        <v>6418187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1425,6 +1425,458 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113497782</v>
+      </c>
+      <c r="B9" t="n">
+        <v>74151</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mollsjönäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>330568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6417875</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113496114</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56785</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djupevik, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>330709</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6418035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113497500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80089</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djupevik, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>330643</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6417894</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113496692</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56785</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djupevik, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>330860</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6418101</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113497853</v>
+        <v>113495813</v>
       </c>
       <c r="B5" t="n">
-        <v>74151</v>
+        <v>95988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330551</v>
+        <v>330577</v>
       </c>
       <c r="R5" t="n">
-        <v>6417874</v>
+        <v>6417835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113496671</v>
+        <v>113497853</v>
       </c>
       <c r="B6" t="n">
-        <v>80089</v>
+        <v>74151</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1130,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330839</v>
+        <v>330551</v>
       </c>
       <c r="R6" t="n">
-        <v>6418137</v>
+        <v>6417874</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113495813</v>
+        <v>113496459</v>
       </c>
       <c r="B7" t="n">
-        <v>95988</v>
+        <v>90067</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330577</v>
+        <v>330713</v>
       </c>
       <c r="R7" t="n">
-        <v>6417835</v>
+        <v>6418187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113496459</v>
+        <v>113496671</v>
       </c>
       <c r="B8" t="n">
-        <v>90067</v>
+        <v>80089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,39 +1336,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330713</v>
+        <v>330839</v>
       </c>
       <c r="R8" t="n">
-        <v>6418187</v>
+        <v>6418137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113497782</v>
+        <v>113497500</v>
       </c>
       <c r="B9" t="n">
-        <v>74151</v>
+        <v>80095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,39 +1439,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330568</v>
+        <v>330643</v>
       </c>
       <c r="R9" t="n">
-        <v>6417875</v>
+        <v>6417894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113496114</v>
+        <v>113497782</v>
       </c>
       <c r="B10" t="n">
-        <v>56785</v>
+        <v>74157</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,39 +1552,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330709</v>
+        <v>330568</v>
       </c>
       <c r="R10" t="n">
-        <v>6418035</v>
+        <v>6417875</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113497500</v>
+        <v>113496114</v>
       </c>
       <c r="B11" t="n">
-        <v>80089</v>
+        <v>56789</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330643</v>
+        <v>330709</v>
       </c>
       <c r="R11" t="n">
-        <v>6417894</v>
+        <v>6418035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,7 +1769,7 @@
         <v>113496692</v>
       </c>
       <c r="B12" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113495813</v>
+        <v>113496459</v>
       </c>
       <c r="B5" t="n">
-        <v>95988</v>
+        <v>90073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330577</v>
+        <v>330713</v>
       </c>
       <c r="R5" t="n">
-        <v>6417835</v>
+        <v>6418187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113497853</v>
+        <v>113496671</v>
       </c>
       <c r="B6" t="n">
-        <v>74151</v>
+        <v>80095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1130,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330551</v>
+        <v>330839</v>
       </c>
       <c r="R6" t="n">
-        <v>6417874</v>
+        <v>6418137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113496459</v>
+        <v>113495813</v>
       </c>
       <c r="B7" t="n">
-        <v>90067</v>
+        <v>95994</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330713</v>
+        <v>330577</v>
       </c>
       <c r="R7" t="n">
-        <v>6418187</v>
+        <v>6417835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113496671</v>
+        <v>113497853</v>
       </c>
       <c r="B8" t="n">
-        <v>80089</v>
+        <v>74157</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,39 +1336,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330839</v>
+        <v>330551</v>
       </c>
       <c r="R8" t="n">
-        <v>6418137</v>
+        <v>6417874</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113496459</v>
+        <v>113495813</v>
       </c>
       <c r="B5" t="n">
-        <v>90073</v>
+        <v>95994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330713</v>
+        <v>330577</v>
       </c>
       <c r="R5" t="n">
-        <v>6418187</v>
+        <v>6417835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113495813</v>
+        <v>113497853</v>
       </c>
       <c r="B7" t="n">
-        <v>95994</v>
+        <v>74157</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330577</v>
+        <v>330551</v>
       </c>
       <c r="R7" t="n">
-        <v>6417835</v>
+        <v>6417874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113497853</v>
+        <v>113496459</v>
       </c>
       <c r="B8" t="n">
-        <v>74157</v>
+        <v>90073</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330551</v>
+        <v>330713</v>
       </c>
       <c r="R8" t="n">
-        <v>6417874</v>
+        <v>6418187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113497500</v>
+        <v>113497782</v>
       </c>
       <c r="B9" t="n">
-        <v>80095</v>
+        <v>74157</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,39 +1439,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330643</v>
+        <v>330568</v>
       </c>
       <c r="R9" t="n">
-        <v>6417894</v>
+        <v>6417875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113497782</v>
+        <v>113496114</v>
       </c>
       <c r="B10" t="n">
-        <v>74157</v>
+        <v>56789</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,39 +1552,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330568</v>
+        <v>330709</v>
       </c>
       <c r="R10" t="n">
-        <v>6417875</v>
+        <v>6418035</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113496114</v>
+        <v>113497500</v>
       </c>
       <c r="B11" t="n">
-        <v>56789</v>
+        <v>80095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330709</v>
+        <v>330643</v>
       </c>
       <c r="R11" t="n">
-        <v>6418035</v>
+        <v>6417894</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>113495813</v>
       </c>
       <c r="B5" t="n">
-        <v>95994</v>
+        <v>96001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113496671</v>
+        <v>113496459</v>
       </c>
       <c r="B6" t="n">
-        <v>80095</v>
+        <v>90080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1130,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330839</v>
+        <v>330713</v>
       </c>
       <c r="R6" t="n">
-        <v>6418137</v>
+        <v>6418187</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
         <v>113497853</v>
       </c>
       <c r="B7" t="n">
-        <v>74157</v>
+        <v>74164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113496459</v>
+        <v>113496671</v>
       </c>
       <c r="B8" t="n">
-        <v>90073</v>
+        <v>80102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,39 +1336,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330713</v>
+        <v>330839</v>
       </c>
       <c r="R8" t="n">
-        <v>6418187</v>
+        <v>6418137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113497782</v>
+        <v>113496692</v>
       </c>
       <c r="B9" t="n">
-        <v>74157</v>
+        <v>56796</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,39 +1439,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330568</v>
+        <v>330860</v>
       </c>
       <c r="R9" t="n">
-        <v>6417875</v>
+        <v>6418101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113496114</v>
+        <v>113497500</v>
       </c>
       <c r="B10" t="n">
-        <v>56789</v>
+        <v>80102</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330709</v>
+        <v>330643</v>
       </c>
       <c r="R10" t="n">
-        <v>6418035</v>
+        <v>6417894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113497500</v>
+        <v>113497782</v>
       </c>
       <c r="B11" t="n">
-        <v>80095</v>
+        <v>74164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,39 +1665,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330643</v>
+        <v>330568</v>
       </c>
       <c r="R11" t="n">
-        <v>6417894</v>
+        <v>6417875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113496692</v>
+        <v>113496114</v>
       </c>
       <c r="B12" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330860</v>
+        <v>330709</v>
       </c>
       <c r="R12" t="n">
-        <v>6418101</v>
+        <v>6418035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113495813</v>
+        <v>113496671</v>
       </c>
       <c r="B5" t="n">
-        <v>96001</v>
+        <v>80104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330577</v>
+        <v>330839</v>
       </c>
       <c r="R5" t="n">
-        <v>6417835</v>
+        <v>6418137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
         <v>113496459</v>
       </c>
       <c r="B6" t="n">
-        <v>90080</v>
+        <v>90083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113497853</v>
+        <v>113495813</v>
       </c>
       <c r="B7" t="n">
-        <v>74164</v>
+        <v>96006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330551</v>
+        <v>330577</v>
       </c>
       <c r="R7" t="n">
-        <v>6417874</v>
+        <v>6417835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113496671</v>
+        <v>113497853</v>
       </c>
       <c r="B8" t="n">
-        <v>80102</v>
+        <v>74166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1336,39 +1336,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330839</v>
+        <v>330551</v>
       </c>
       <c r="R8" t="n">
-        <v>6418137</v>
+        <v>6417874</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
         <v>113496692</v>
       </c>
       <c r="B9" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>113497500</v>
       </c>
       <c r="B10" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113497782</v>
+        <v>113496114</v>
       </c>
       <c r="B11" t="n">
-        <v>74164</v>
+        <v>56798</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,39 +1665,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330568</v>
+        <v>330709</v>
       </c>
       <c r="R11" t="n">
-        <v>6417875</v>
+        <v>6418035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113496114</v>
+        <v>113497782</v>
       </c>
       <c r="B12" t="n">
-        <v>56796</v>
+        <v>74166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330709</v>
+        <v>330568</v>
       </c>
       <c r="R12" t="n">
-        <v>6418035</v>
+        <v>6417875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>113496671</v>
       </c>
       <c r="B5" t="n">
-        <v>80104</v>
+        <v>80132</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>113496459</v>
       </c>
       <c r="B6" t="n">
-        <v>90083</v>
+        <v>90114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>113495813</v>
       </c>
       <c r="B7" t="n">
-        <v>96006</v>
+        <v>96034</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>113497853</v>
       </c>
       <c r="B8" t="n">
-        <v>74166</v>
+        <v>74194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>113496692</v>
       </c>
       <c r="B9" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113497500</v>
+        <v>113497782</v>
       </c>
       <c r="B10" t="n">
-        <v>80104</v>
+        <v>74194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,39 +1552,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330643</v>
+        <v>330568</v>
       </c>
       <c r="R10" t="n">
-        <v>6417894</v>
+        <v>6417875</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,7 @@
         <v>113496114</v>
       </c>
       <c r="B11" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113497782</v>
+        <v>113497500</v>
       </c>
       <c r="B12" t="n">
-        <v>74166</v>
+        <v>80132</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,39 +1778,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6428</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330568</v>
+        <v>330643</v>
       </c>
       <c r="R12" t="n">
-        <v>6417875</v>
+        <v>6417894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113496671</v>
+        <v>113497853</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>74194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>6428</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330839</v>
+        <v>330551</v>
       </c>
       <c r="R5" t="n">
-        <v>6418137</v>
+        <v>6417874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113496459</v>
+        <v>113495813</v>
       </c>
       <c r="B6" t="n">
-        <v>90114</v>
+        <v>96034</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330713</v>
+        <v>330577</v>
       </c>
       <c r="R6" t="n">
-        <v>6418187</v>
+        <v>6417835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113495813</v>
+        <v>113496671</v>
       </c>
       <c r="B7" t="n">
-        <v>96034</v>
+        <v>80132</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,39 +1233,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330577</v>
+        <v>330839</v>
       </c>
       <c r="R7" t="n">
-        <v>6417835</v>
+        <v>6418137</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113497853</v>
+        <v>113496459</v>
       </c>
       <c r="B8" t="n">
-        <v>74194</v>
+        <v>90115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330551</v>
+        <v>330713</v>
       </c>
       <c r="R8" t="n">
-        <v>6417874</v>
+        <v>6418187</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113496114</v>
+        <v>113497500</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>80132</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330709</v>
+        <v>330643</v>
       </c>
       <c r="R11" t="n">
-        <v>6418035</v>
+        <v>6417894</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113497500</v>
+        <v>113496114</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>56826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330643</v>
+        <v>330709</v>
       </c>
       <c r="R12" t="n">
-        <v>6417894</v>
+        <v>6418035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1121,7 +1121,7 @@
         <v>113495813</v>
       </c>
       <c r="B6" t="n">
-        <v>96034</v>
+        <v>96038</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>113496459</v>
       </c>
       <c r="B8" t="n">
-        <v>90115</v>
+        <v>90119</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113497500</v>
+        <v>113496114</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330643</v>
+        <v>330709</v>
       </c>
       <c r="R11" t="n">
-        <v>6417894</v>
+        <v>6418035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113496114</v>
+        <v>113497500</v>
       </c>
       <c r="B12" t="n">
-        <v>56826</v>
+        <v>80132</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330709</v>
+        <v>330643</v>
       </c>
       <c r="R12" t="n">
-        <v>6418035</v>
+        <v>6417894</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113497853</v>
+        <v>113496459</v>
       </c>
       <c r="B5" t="n">
-        <v>74194</v>
+        <v>90119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,35 +1031,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6428</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330551</v>
+        <v>330713</v>
       </c>
       <c r="R5" t="n">
-        <v>6417874</v>
+        <v>6418187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113495813</v>
+        <v>113497853</v>
       </c>
       <c r="B6" t="n">
-        <v>96038</v>
+        <v>74194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330577</v>
+        <v>330551</v>
       </c>
       <c r="R6" t="n">
-        <v>6417835</v>
+        <v>6417874</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113496459</v>
+        <v>113495813</v>
       </c>
       <c r="B8" t="n">
-        <v>90119</v>
+        <v>96038</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330713</v>
+        <v>330577</v>
       </c>
       <c r="R8" t="n">
-        <v>6418187</v>
+        <v>6417835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113496692</v>
+        <v>113496114</v>
       </c>
       <c r="B9" t="n">
         <v>56826</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330860</v>
+        <v>330709</v>
       </c>
       <c r="R9" t="n">
-        <v>6418101</v>
+        <v>6418035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113497782</v>
+        <v>113496692</v>
       </c>
       <c r="B10" t="n">
-        <v>74194</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,39 +1552,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330568</v>
+        <v>330860</v>
       </c>
       <c r="R10" t="n">
-        <v>6417875</v>
+        <v>6418101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113496114</v>
+        <v>113497782</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>74194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,39 +1665,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330709</v>
+        <v>330568</v>
       </c>
       <c r="R11" t="n">
-        <v>6418035</v>
+        <v>6417875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113496459</v>
+        <v>113496671</v>
       </c>
       <c r="B5" t="n">
-        <v>90119</v>
+        <v>80132</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4660</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330713</v>
+        <v>330839</v>
       </c>
       <c r="R5" t="n">
-        <v>6418187</v>
+        <v>6418137</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113497853</v>
+        <v>113495813</v>
       </c>
       <c r="B6" t="n">
-        <v>74194</v>
+        <v>96038</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330551</v>
+        <v>330577</v>
       </c>
       <c r="R6" t="n">
-        <v>6417874</v>
+        <v>6417835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113496671</v>
+        <v>113496459</v>
       </c>
       <c r="B7" t="n">
-        <v>80132</v>
+        <v>90119</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,39 +1233,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>4660</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330839</v>
+        <v>330713</v>
       </c>
       <c r="R7" t="n">
-        <v>6418137</v>
+        <v>6418187</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113495813</v>
+        <v>113497853</v>
       </c>
       <c r="B8" t="n">
-        <v>96038</v>
+        <v>74194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330577</v>
+        <v>330551</v>
       </c>
       <c r="R8" t="n">
-        <v>6417835</v>
+        <v>6417874</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113496671</v>
+        <v>113496459</v>
       </c>
       <c r="B5" t="n">
-        <v>80132</v>
+        <v>90119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1027,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sandsjöberg (Sandsjöberg), Vg</t>
+          <t>Djupevik (Djupevik), Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>330839</v>
+        <v>330713</v>
       </c>
       <c r="R5" t="n">
-        <v>6418137</v>
+        <v>6418187</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113495813</v>
+        <v>113496671</v>
       </c>
       <c r="B6" t="n">
-        <v>96038</v>
+        <v>80132</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,39 +1130,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2606</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390 , Vg</t>
+          <t>Sandsjöberg (Sandsjöberg), Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>330577</v>
+        <v>330839</v>
       </c>
       <c r="R6" t="n">
-        <v>6417835</v>
+        <v>6418137</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113496459</v>
+        <v>113497853</v>
       </c>
       <c r="B7" t="n">
-        <v>90119</v>
+        <v>74194</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,35 +1237,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4660</v>
+        <v>6428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupevik (Djupevik), Vg</t>
+          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>330713</v>
+        <v>330551</v>
       </c>
       <c r="R7" t="n">
-        <v>6418187</v>
+        <v>6417874</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113497853</v>
+        <v>113495813</v>
       </c>
       <c r="B8" t="n">
-        <v>74194</v>
+        <v>96038</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,35 +1340,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mollsjönäs 390  (Mollsjönäs 390 ), Vg</t>
+          <t>Mollsjönäs 390 , Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>330551</v>
+        <v>330577</v>
       </c>
       <c r="R8" t="n">
-        <v>6417874</v>
+        <v>6417835</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113496114</v>
+        <v>113497782</v>
       </c>
       <c r="B9" t="n">
-        <v>56826</v>
+        <v>74194</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,39 +1439,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330709</v>
+        <v>330568</v>
       </c>
       <c r="R9" t="n">
-        <v>6418035</v>
+        <v>6417875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113497782</v>
+        <v>113496114</v>
       </c>
       <c r="B11" t="n">
-        <v>74194</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,39 +1665,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330568</v>
+        <v>330709</v>
       </c>
       <c r="R11" t="n">
-        <v>6417875</v>
+        <v>6418035</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113497782</v>
+        <v>113496114</v>
       </c>
       <c r="B9" t="n">
-        <v>74194</v>
+        <v>56826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,39 +1439,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mollsjönäs, Vg</t>
+          <t>Djupevik, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>330568</v>
+        <v>330709</v>
       </c>
       <c r="R9" t="n">
-        <v>6417875</v>
+        <v>6418035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113496692</v>
+        <v>113497500</v>
       </c>
       <c r="B10" t="n">
-        <v>56826</v>
+        <v>80132</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>330860</v>
+        <v>330643</v>
       </c>
       <c r="R10" t="n">
-        <v>6418101</v>
+        <v>6417894</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113496114</v>
+        <v>113497782</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>74194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,39 +1665,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupevik, Vg</t>
+          <t>Mollsjönäs, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>330709</v>
+        <v>330568</v>
       </c>
       <c r="R11" t="n">
-        <v>6418035</v>
+        <v>6417875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,10 +1766,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113497500</v>
+        <v>113496692</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>56826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1782,21 +1782,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>330643</v>
+        <v>330860</v>
       </c>
       <c r="R12" t="n">
-        <v>6417894</v>
+        <v>6418101</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>121768106</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 40983-2023 artfynd.xlsx
+++ b/artfynd/A 40983-2023 artfynd.xlsx
@@ -1882,7 +1882,7 @@
         <v>121768106</v>
       </c>
       <c r="B13" t="n">
-        <v>57381</v>
+        <v>57385</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
